--- a/CVS_credit_model.xlsx
+++ b/CVS_credit_model.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prepared by: Archit Chawla  |  Date: October 20, 2026  |  Independent research project — not investment advice and not a credit rating.</t>
+          <t>Prepared by: Archit Chawla  |  Independent research project — not investment advice and not a credit rating.</t>
         </is>
       </c>
     </row>
